--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.505951749512255</v>
+        <v>1.219717159295742</v>
       </c>
       <c r="D2" t="n">
-        <v>12.93469121602565</v>
+        <v>2.101887322604168</v>
       </c>
       <c r="E2" t="n">
-        <v>7.887740556183397</v>
+        <v>1.281757840379802</v>
       </c>
       <c r="F2" t="n">
-        <v>4.995157382325703</v>
+        <v>0.8117130746279269</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.57897618419622</v>
+        <v>3.344083629931886</v>
       </c>
       <c r="D3" t="n">
-        <v>23.11492078534684</v>
+        <v>3.756174627618862</v>
       </c>
       <c r="E3" t="n">
-        <v>7.887740556183397</v>
+        <v>1.281757840379802</v>
       </c>
       <c r="F3" t="n">
-        <v>4.995157382325703</v>
+        <v>0.8117130746279269</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.88365764604814</v>
+        <v>3.881094367482823</v>
       </c>
       <c r="D4" t="n">
-        <v>23.95820446113127</v>
+        <v>3.893208224933832</v>
       </c>
       <c r="E4" t="n">
-        <v>7.887740556183397</v>
+        <v>1.281757840379802</v>
       </c>
       <c r="F4" t="n">
-        <v>4.995157382325703</v>
+        <v>0.8117130746279269</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.80314979886199</v>
+        <v>4.680511842315074</v>
       </c>
       <c r="D5" t="n">
-        <v>14.28506438495296</v>
+        <v>2.321322962554856</v>
       </c>
       <c r="E5" t="n">
-        <v>7.887740556183397</v>
+        <v>1.281757840379802</v>
       </c>
       <c r="F5" t="n">
-        <v>4.995157382325703</v>
+        <v>0.8117130746279269</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
